--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488235_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488235_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2003</v>
+        <v>8.678800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4983</v>
+        <v>5.9521</v>
       </c>
       <c r="F2" t="n">
-        <v>2.702</v>
+        <v>2.7267</v>
       </c>
       <c r="G2" t="n">
         <v>3.9526</v>
@@ -610,13 +610,13 @@
         <v>3.891</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0619</v>
+        <v>0.5403</v>
       </c>
       <c r="T2" t="n">
-        <v>3.712</v>
+        <v>1.1659</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6502</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>2.5183</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7879</v>
+        <v>2.8158</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7441</v>
+        <v>-0.2977</v>
       </c>
       <c r="F3" t="n">
-        <v>3.532</v>
+        <v>3.1135</v>
       </c>
       <c r="G3" t="n">
         <v>0.7517</v>
@@ -688,13 +688,13 @@
         <v>4.2616</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0923</v>
+        <v>-1.0645</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.664</v>
+        <v>-0.2176</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4283</v>
+        <v>-0.8469</v>
       </c>
       <c r="V3" t="n">
         <v>2.2022</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8526</v>
+        <v>0.5734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8155</v>
+        <v>0.1012</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0371</v>
+        <v>0.4721</v>
       </c>
       <c r="G4" t="n">
-        <v>1.738</v>
+        <v>0.9361</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8258</v>
+        <v>2.2969</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5638</v>
+        <v>-1.3608</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0095</v>
+        <v>1.0102</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3366</v>
+        <v>1.5802</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3271</v>
+        <v>-0.5699</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7475</v>
+        <v>-0.0741</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5107</v>
+        <v>0.7167</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2367</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.297</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4095</v>
+        <v>-0.8456</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8081</v>
+        <v>0.2027</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6012999999999999</v>
+        <v>-1.0483</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.7771</v>
+        <v>-0.6289</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.091</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5356</v>
+        <v>0.4699</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7369</v>
+        <v>-1.3735</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2013</v>
+        <v>1.8434</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9361</v>
+        <v>1.3122</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2969</v>
+        <v>0.1892</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3608</v>
+        <v>1.123</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0102</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5802</v>
+        <v>1.2366</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5699</v>
+        <v>-0.5284</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0741</v>
+        <v>0.604</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7167</v>
+        <v>-1.0474</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7907999999999999</v>
+        <v>1.6514</v>
       </c>
       <c r="P5" t="n">
         <v>1.1117</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1117</v>
+        <v>-2.2234</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2234</v>
+        <v>3.3352</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9546</v>
+        <v>-1.0085</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6354</v>
+        <v>-0.1716</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3192</v>
+        <v>-0.8369</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6289</v>
+        <v>-0.9455</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3133</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9077</v>
+        <v>0.0926</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6034</v>
+        <v>-0.4028</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6957</v>
+        <v>0.4954</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3122</v>
+        <v>1.738</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1892</v>
+        <v>-0.8258</v>
       </c>
       <c r="I6" t="n">
-        <v>1.123</v>
+        <v>2.5638</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7082000000000001</v>
+        <v>-0.0095</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2366</v>
+        <v>-1.3366</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5284</v>
+        <v>1.3271</v>
       </c>
       <c r="M6" t="n">
-        <v>0.604</v>
+        <v>1.7475</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0474</v>
+        <v>0.5107</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6514</v>
+        <v>1.2367</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2234</v>
+        <v>-1.297</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3352</v>
+        <v>2.7793</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.3861</v>
+        <v>0.6494</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4014</v>
+        <v>0.5898</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9847</v>
+        <v>0.0597</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9455</v>
+        <v>-3.7771</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3133</v>
+        <v>0.3139</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2589</v>
+        <v>-4.091</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3117</v>
+        <v>-3.3745</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.8145</v>
+        <v>-5.0743</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5028</v>
+        <v>1.6998</v>
       </c>
       <c r="G8" t="n">
         <v>-4.9851</v>
@@ -1078,13 +1078,13 @@
         <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8646</v>
+        <v>-0.9274</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0184</v>
+        <v>-0.2782</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8461</v>
+        <v>-0.6491</v>
       </c>
       <c r="V8" t="n">
         <v>0.3144</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.31</v>
+        <v>-4.2064</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.9647</v>
+        <v>-5.1812</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.9748</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1546</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8583</v>
+        <v>-0.7548</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0396</v>
+        <v>-0.2561</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8188</v>
+        <v>-0.4987</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,25 +1189,25 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.3361</v>
+        <v>3.609900000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.530599999999998</v>
+        <v>-7.257</v>
       </c>
       <c r="F10" t="n">
-        <v>10.8667</v>
+        <v>10.8668</v>
       </c>
       <c r="G10" t="n">
         <v>0.2207000000000008</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7885</v>
+        <v>5.788500000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.568000000000001</v>
+        <v>-5.568</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.151</v>
+        <v>-1.151000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>5.570600000000001</v>
@@ -1219,13 +1219,13 @@
         <v>1.3717</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2179000000000001</v>
+        <v>0.2178999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1.1537</v>
       </c>
       <c r="P10" t="n">
-        <v>7.4114</v>
+        <v>7.411399999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>-13.8965</v>
@@ -1234,13 +1234,13 @@
         <v>21.308</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.979200000000001</v>
+        <v>-3.7058</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5972</v>
+        <v>0.8707999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.5766</v>
+        <v>-4.5763</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3166000000000002</v>
@@ -1249,13 +1249,13 @@
         <v>6.9198</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.236499999999999</v>
+        <v>-7.2365</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.2043</v>
+        <v>3.6236</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0429</v>
+        <v>2.9108</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1614</v>
+        <v>0.7128</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1547</v>
+        <v>1.56</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0574</v>
+        <v>-1.1862</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2121</v>
+        <v>2.7461</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5593</v>
+        <v>1.7017</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4764</v>
+        <v>-0.1765</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0829</v>
+        <v>1.8781</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5953000000000001</v>
+        <v>-0.1417</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-1.0097</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1292</v>
+        <v>0.868</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2523</v>
+        <v>0.1928</v>
       </c>
       <c r="T11" t="n">
-        <v>2.41</v>
+        <v>0.1356</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8423</v>
+        <v>0.0572</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5733</v>
+        <v>0.9444</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5733</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0963</v>
+        <v>1.9142</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7357</v>
+        <v>-0.9815</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3606</v>
+        <v>2.8957</v>
       </c>
       <c r="G12" t="n">
-        <v>1.56</v>
+        <v>1.5127</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1862</v>
+        <v>-0.3058</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7461</v>
+        <v>1.8186</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7017</v>
+        <v>0.0677</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1765</v>
+        <v>-0.5757</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8781</v>
+        <v>0.6434</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1417</v>
+        <v>1.445</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0097</v>
+        <v>0.2699</v>
       </c>
       <c r="O12" t="n">
-        <v>0.868</v>
+        <v>1.1751</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3346</v>
+        <v>0.1421</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0396</v>
+        <v>0.0625</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.295</v>
+        <v>0.0796</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9444</v>
+        <v>0.63</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4235</v>
+        <v>1.5458</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2753</v>
+        <v>0.574</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6987</v>
+        <v>0.9719</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5127</v>
+        <v>1.1547</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3058</v>
+        <v>-0.0574</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8186</v>
+        <v>1.2121</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0677</v>
+        <v>0.5593</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5757</v>
+        <v>0.4764</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6434</v>
+        <v>0.0829</v>
       </c>
       <c r="M13" t="n">
-        <v>1.445</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2699</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1751</v>
+        <v>1.1292</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3487</v>
+        <v>1.5939</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2313</v>
+        <v>0.9411</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1174</v>
+        <v>0.6528</v>
       </c>
       <c r="V13" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8878</v>
+        <v>1.0093</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3843</v>
+        <v>0.6781</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.3312</v>
       </c>
       <c r="G14" t="n">
         <v>1.3609</v>
@@ -1546,13 +1546,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0828</v>
+        <v>0.2043</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2313</v>
+        <v>0.0625</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3141</v>
+        <v>0.1418</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4877</v>
+        <v>0.2789</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5499000000000001</v>
+        <v>0.0364</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0622</v>
+        <v>0.2425</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8887</v>
+        <v>-2.8173</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3295</v>
+        <v>-0.7742</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5592</v>
+        <v>-2.0432</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5255</v>
+        <v>-2.055</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4426</v>
+        <v>0.4415</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0829</v>
+        <v>-2.4965</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3632</v>
+        <v>-0.7624</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1131</v>
+        <v>-1.2157</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4763</v>
+        <v>0.4533</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8529</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9646</v>
+        <v>-2.0382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3642</v>
+        <v>0.0053</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8891</v>
+        <v>0.3535</v>
       </c>
       <c r="U15" t="n">
-        <v>0.475</v>
+        <v>-0.3482</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8877</v>
+        <v>3.4616</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.776</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8877</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7711</v>
+        <v>-0.0856</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0625</v>
+        <v>-2.377</v>
       </c>
       <c r="F16" t="n">
         <v>2.2915</v>
@@ -1702,10 +1702,10 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3793</v>
+        <v>0.3062</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2984</v>
+        <v>0.3871</v>
       </c>
       <c r="U16" t="n">
         <v>-0.0809</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VINCENT MAGO</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.0277</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.203</v>
+        <v>-0.8437</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3386</v>
+        <v>-0.184</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4159</v>
+        <v>1.8887</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.618</v>
+        <v>1.3295</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0339</v>
+        <v>0.5592</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5953000000000001</v>
+        <v>1.5255</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4294</v>
+        <v>1.4426</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1659</v>
+        <v>0.0829</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1794</v>
+        <v>0.3632</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0474</v>
+        <v>-0.1131</v>
       </c>
       <c r="O17" t="n">
-        <v>0.868</v>
+        <v>0.4763</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2234</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.891</v>
+        <v>-2.9646</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9431</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7783</v>
+        <v>0.5954</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8352000000000001</v>
+        <v>0.2288</v>
       </c>
       <c r="V17" t="n">
+        <v>-1.8877</v>
+      </c>
+      <c r="W17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" t="n">
-        <v>0.3144</v>
-      </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9781</v>
+        <v>-1.3514</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0408</v>
+        <v>-3.9929</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06270000000000001</v>
+        <v>2.6414</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8173</v>
+        <v>0.3557</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7742</v>
+        <v>1.073</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0432</v>
+        <v>-0.7173</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.055</v>
+        <v>0.0271</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4415</v>
+        <v>1.8506</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.4965</v>
+        <v>-1.8235</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7624</v>
+        <v>0.3286</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2157</v>
+        <v>-0.7775</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4533</v>
+        <v>1.1062</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3706</v>
+        <v>-2.594</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0382</v>
+        <v>-4.8175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2518</v>
+        <v>0.8863</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7237</v>
+        <v>0.7981</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.528</v>
+        <v>0.0883</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4616</v>
+        <v>0.0005</v>
       </c>
       <c r="W18" t="n">
-        <v>3.776</v>
+        <v>-0.0005</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>R. VINCENT MAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1636</v>
+        <v>-1.7114</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6991</v>
+        <v>-2.4761</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5355</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3557</v>
+        <v>0.4159</v>
       </c>
       <c r="H19" t="n">
-        <v>1.073</v>
+        <v>-0.618</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7173</v>
+        <v>1.0339</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0271</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8506</v>
+        <v>0.4294</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8235</v>
+        <v>0.1659</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3286</v>
+        <v>-0.1794</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7775</v>
+        <v>-1.0474</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1062</v>
+        <v>0.868</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.594</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8175</v>
+        <v>-3.891</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0742</v>
+        <v>0.0961</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0919</v>
+        <v>0.5052</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0177</v>
+        <v>-0.4091</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0011</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.6832</v>
+        <v>-6.8791</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1991</v>
+        <v>-4.395</v>
       </c>
       <c r="F20" t="n">
         <v>-2.4841</v>
@@ -2014,10 +2014,10 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>0.577</v>
+        <v>0.3811</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9314</v>
+        <v>0.7356</v>
       </c>
       <c r="U20" t="n">
         <v>-0.3544</v>
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3362</v>
+        <v>-2.683400000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.8668</v>
+        <v>-10.8669</v>
       </c>
       <c r="F21" t="n">
-        <v>7.5306</v>
+        <v>8.1835</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2206999999999999</v>
+        <v>-0.2207000000000008</v>
       </c>
       <c r="H21" t="n">
         <v>-5.7886</v>
       </c>
       <c r="I21" t="n">
-        <v>5.567799999999999</v>
+        <v>5.567800000000001</v>
       </c>
       <c r="J21" t="n">
         <v>-1.3719</v>
@@ -2080,10 +2080,10 @@
         <v>-5.5704</v>
       </c>
       <c r="O21" t="n">
-        <v>6.7215</v>
+        <v>6.721500000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.4115</v>
+        <v>-7.411499999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-21.308</v>
@@ -2092,16 +2092,16 @@
         <v>13.8965</v>
       </c>
       <c r="S21" t="n">
-        <v>3.979200000000001</v>
+        <v>4.632199999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>4.5764</v>
+        <v>4.5766</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5971999999999998</v>
+        <v>0.05590000000000012</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3167</v>
+        <v>0.3166999999999995</v>
       </c>
       <c r="W21" t="n">
         <v>7.236499999999999</v>
